--- a/experiment3/data_processing/exp_data/06_trimmed.xlsx
+++ b/experiment3/data_processing/exp_data/06_trimmed.xlsx
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>747.6190476190476</v>
+        <v>712.3157894736842</v>
       </c>
     </row>
     <row r="61">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>738.9677419354839</v>
+        <v>740.2758620689655</v>
       </c>
     </row>
     <row r="62">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>770.2692307692307</v>
+        <v>768.5833333333334</v>
       </c>
     </row>
     <row r="66">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>448.5625</v>
+        <v>449.0333333333334</v>
       </c>
     </row>
     <row r="80">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>413.4285714285714</v>
+        <v>405.4444444444445</v>
       </c>
     </row>
     <row r="92">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>743.3478260869565</v>
+        <v>726.9545454545455</v>
       </c>
     </row>
     <row r="147">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>690.64</v>
+        <v>643.5909090909091</v>
       </c>
     </row>
     <row r="158">
